--- a/example/reference_results/8_microbial_load_correction/microbial_load_correction_summary.xlsx
+++ b/example/reference_results/8_microbial_load_correction/microbial_load_correction_summary.xlsx
@@ -243,7 +243,7 @@
     <t xml:space="preserve">Phyloseq_Version</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 15:16:29 CEST</t>
+    <t xml:space="preserve">2026-09-29 16:47:32 CEST</t>
   </si>
   <si>
     <t xml:space="preserve">/Users/amro/Documents/workflows/DADA2_16S_Illumina_PairedEnd_Workflow/example/run_results/7_copy_number_correction/copy_number_corrected_asv_count_table.csv</t>
@@ -252,7 +252,7 @@
     <t xml:space="preserve">c947e7664fb75efd061c5c8de721b7e8</t>
   </si>
   <si>
-    <t xml:space="preserve">143355f48ec0fd4be6486a49b09480fa</t>
+    <t xml:space="preserve">17f2c4800567a35d794771c3b6a3de3e</t>
   </si>
   <si>
     <t xml:space="preserve">/Users/amro/Documents/workflows/DADA2_16S_Illumina_PairedEnd_Workflow/example/data/cell_count/cell_count.tsv</t>

--- a/example/reference_results/8_microbial_load_correction/microbial_load_correction_summary.xlsx
+++ b/example/reference_results/8_microbial_load_correction/microbial_load_correction_summary.xlsx
@@ -246,7 +246,7 @@
     <t xml:space="preserve">2026-09-29 16:47:32 CEST</t>
   </si>
   <si>
-    <t xml:space="preserve">/Users/amro/Documents/workflows/DADA2_16S_Illumina_PairedEnd_Workflow/example/run_results/7_copy_number_correction/copy_number_corrected_asv_count_table.csv</t>
+    <t xml:space="preserve">example/run_results/7_copy_number_correction/copy_number_corrected_asv_count_table.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c947e7664fb75efd061c5c8de721b7e8</t>
@@ -255,7 +255,7 @@
     <t xml:space="preserve">17f2c4800567a35d794771c3b6a3de3e</t>
   </si>
   <si>
-    <t xml:space="preserve">/Users/amro/Documents/workflows/DADA2_16S_Illumina_PairedEnd_Workflow/example/data/cell_count/cell_count.tsv</t>
+    <t xml:space="preserve">example/data/cell_count/cell_count.tsv</t>
   </si>
   <si>
     <t xml:space="preserve">78afd1757a5c63fa4a6c31bca450fe7b</t>
